--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-014_ユーザー管理_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-014_ユーザー管理_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="15535275"/>
+    <ext cx="8572500" cy="15735300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-014 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-014 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限8時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更・承認待ち申請の承認者付け替え。</t>
+          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限2時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更のサーバー側実施（画面側は ONL-023 で実装済み）・承認待ち申請の承認者付け替え。</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="94" customHeight="1">
+    <row r="3" ht="229" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2362,7 +2362,11 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：メールアドレスを trim＋toLowerCase(Locale.ROOT) で正規化して保存・検索（existsByEmail / existsByEmailAndIdNot に変更）、未定義だった private notFound() ほかの補助メソッドの定義を追加、@EnableMethodSecurity / handleAccessDenied / handleTypeMismatch を ONL-001 の共通基盤への追加改修に集約（本処理での追加を削除）、updated_at をトリガ自動更新に変更</t>
+          <t>・確定設計変更 D1〜D10 を反映：メールアドレスを trim＋toLowerCase(Locale.ROOT) で正規化して保存・検索（existsByEmail / existsByEmailAndIdNot に変更）、未定義だった private notFound() ほかの補助メソッドの定義を追加、@EnableMethodSecurity / handleAccessDenied / handleTypeMismatch を ONL-001 の共通基盤への追加改修に集約（本処理での追加を削除）、updated_at をトリガ自動更新に変更
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・初期パスワード・再設定パスワードを設定したユーザーは must_change_password=true にし、初回ログイン時にパスワード変更を強制する（ONL-001/023 のサーバー側強制と連動。「MVPでは未実装」を撤回）
+・パスワード再設定は failed_login_count=0 / locked_until=NULL も行い、アカウントロックの解除を兼ねる
+・EmailNormalizer（trim + 小文字化）を util パッケージに追加</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -5448,7 +5452,7 @@
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="169" customHeight="1">
+    <row r="21" ht="154" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -5458,11 +5462,11 @@
         <is>
           <t>@PostMapping
 @ResponseStatus(HttpStatus.CREATED)
-public UserDetailResponse create(@Valid @RequestBody UserCreateRequest request, @AuthenticationPrincipal Jwt jwt)
+public UserDetailResponse create(@Valid @RequestBody UserCreateRequest request, Authentication auth)
 @PutMapping("/{id}")
-public UserDetailResponse update(@PathVariable Long id, @Valid @RequestBody UserUpdateRequest request, @AuthenticationPrincipal Jwt jwt)
+public UserDetailResponse update(@PathVariable Long id, @Valid @RequestBody UserUpdateRequest request, Authentication auth)
 @PutMapping("/{id}/password")
-public UserDetailResponse resetPassword(@PathVariable Long id, @Valid @RequestBody PasswordResetRequest request, @AuthenticationPrincipal Jwt jwt)</t>
+public UserDetailResponse resetPassword(@PathVariable Long id, @Valid @RequestBody PasswordResetRequest request, Authentication auth)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
@@ -5565,17 +5569,17 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub = 操作者の users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Long actorId = Long.valueOf(jwt.getSubject());      // 操作者（自己保護の判定に使う）
+          <t>Long actorId = Long.valueOf(auth.getName());      // 操作者（自己保護の判定に使う）
 return userService.create(request, actorId);              // update(id, request, actorId) / resetPassword(id, request, actorId)</t>
         </is>
       </c>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-014_ユーザー管理_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-014_ユーザー管理_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="15735300"/>
+    <ext cx="8572500" cy="16173450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-014 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-014 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E29"/>
+  <dimension ref="A2:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -835,405 +835,429 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="49" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
+          <t>E-001</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>認証が必要です。再度ログインしてください。</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>トークンなし・不正・期限切れ／パスワード変更・再設定より前に発行されたトークン／ユーザーが INACTIVE・存在しない（ActiveUserFilter）</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>AuthenticationEntryPoint／ActiveUserFilter（ONL-001）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="94" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
           <t>E-002</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>項目別メッセージ（4. 参照）／入力内容が正しくありません。</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>入力チェック不正／JSON 不正／パラメータ型不正／検索条件の不正値</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>@Valid／UserService#search／GlobalExceptionHandler</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>項目別メッセージ（4. 参照）／入力内容が正しくありません。／パスワード方針：「新しいパスワードは12文字以上で入力してください。」「新しいパスワードが長すぎます（半角で72文字以内にしてください）。」「新しいパスワードは半角の英字と数字を両方含めてください。」</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>入力チェック不正／JSON 不正／パラメータ型不正／検索条件の不正値／パスワードが方針（12文字以上・英字と数字・72バイト以内）を満たさない</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>@Valid／UserService#search／UserService#checkPolicy／GlobalExceptionHandler</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>E-010</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>この操作を行う権限がありません。</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>ADMIN 以外が呼出し／自分自身の無効化・ロール降格</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>@PreAuthorize／UserService#update</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7" ht="49" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>E-013</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>{項目名}は既に登録されています。（例：メールアドレスは既に登録されています。）</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>メールアドレスが既存ユーザーと重複（正規化＝trim＋小文字化後に一致）／同時登録による一意制約違反</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>UserService#create, update</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>E-014</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>{項目名}の指定が正しくありません。（例：上長の指定が正しくありません。）</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>所属が存在しない／上長が自己・不存在・非ACTIVE・承認権限なし・循環</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>UserService#validateDepartment, validateManager</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>E-014</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>{項目名}の指定が正しくありません。（例：上長の指定が正しくありません。）</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>所属が存在しない／上長が自己・不存在・非ACTIVE・承認権限なし・循環</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>UserService#validateDepartment, validateManager</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>E-015</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>対象のデータが見つかりません。</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>id のユーザーが存在しない</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>UserService#get, update, resetPassword</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="49" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="10" ht="49" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>E-016</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>{理由}ため、この操作は行えません。（例：有効な部下が設定されているため、この操作は行えません。）</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>有効な部下がいるユーザーを無効化／EMPLOYEE に降格</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>UserService#update</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>E-012</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>上記以外の予期しない例外（DB 接続断など）</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler#handleOther</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="49" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>E-019</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>初期パスワードのままです。先にパスワードを変更してください。</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>操作者の JWT が must_change_password=TRUE（claim mcp=true）のまま本 API を呼んだ（PUT /api/auth/password 以外はすべて拒否）</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>PasswordChangeRequiredFilter（ONL-001）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>8.2 ログ出力</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>出力内容</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>出力禁止</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>出力箇所</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>登録成功</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>User created: id, role, actorId</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>メールアドレス・氏名・パスワード</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>UserService#create</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>変更・無効化成功</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>User updated: id, status, role, actorId</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>メールアドレス・氏名</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>UserService#update</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>パスワード設定成功</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>User password reset: id, actorId</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>パスワード・ハッシュ</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>UserService#resetPassword</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>変更・無効化成功</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>User updated: id, status, role, actorId</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>メールアドレス・氏名</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>UserService#update</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>パスワード設定成功</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>User password reset: id, actorId</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>パスワード・ハッシュ</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>UserService#resetPassword</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>上長の循環を検出</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Manager chain cycle: targetId, managerId</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>UserService#validateManager</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="49" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20" ht="49" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>予期しない例外（E-012）</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Unexpected error ＋スタックトレース</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>パスワード・ハッシュ・リクエスト本文</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>8.3 セキュリティ・権限上の考慮</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Controller クラスの @PreAuthorize("hasRole('ADMIN')") で全 5 操作を ADMIN に限定（KF-BD-004）。画面の非表示に頼らず必ずサーバーで検証する。SecurityConfig に @EnableMethodSecurity が必要。非管理者は E-010 / 403。</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>自己保護</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>操作者は自分自身を無効化・ロール降格できない（E-010）。これにより有効な ADMIN が 0 人になることを防ぐ。</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="10" t="n"/>
@@ -1241,27 +1265,27 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>承認ルートの整合</t>
+          <t>権限</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>上長は自己参照禁止・循環禁止・ACTIVE かつ MANAGER/ADMIN のみ。有効な部下がいるユーザーの無効化・EMPLOYEE 降格は禁止（E-016）。</t>
+          <t>Controller クラスの @PreAuthorize("hasRole('ADMIN')") で全 5 操作を ADMIN に限定（KF-BD-004）。画面の非表示に頼らず必ずサーバーで検証する。SecurityConfig に @EnableMethodSecurity が必要。非管理者は E-010 / 403。</t>
         </is>
       </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="10" t="n"/>
     </row>
-    <row r="24" ht="34" customHeight="1">
+    <row r="24" ht="19" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>パスワード</t>
+          <t>自己保護</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>BCrypt でハッシュ化して保存。平文は DTO 内のみで、ログ・応答に出さない。8〜72文字の ASCII（BCrypt の72バイト上限を超えない）。応答に password_hash を含めない。</t>
+          <t>操作者は自分自身を無効化・ロール降格できない（E-010）。これにより有効な ADMIN が 0 人になることを防ぐ。</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -1271,42 +1295,42 @@
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>排他制御</t>
+          <t>承認ルートの整合</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>変更・パスワード設定は SELECT ... FOR UPDATE で対象行を直列化（最後の更新が勝つ。楽観ロック用の列は無い）。メール重複は事前確認＋DB の UNIQUE 制約で二重に防ぎ、同時登録の競合は E-013 に変換する。</t>
+          <t>上長は自己参照禁止・循環禁止・ACTIVE かつ MANAGER/ADMIN のみ。有効な部下がいるユーザーの無効化・EMPLOYEE 降格は禁止（E-016）。</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="10" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1">
+    <row r="26" ht="49" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>二重実行</t>
+          <t>パスワード</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>登録の二重送信（ボタン連打）は UNIQUE 制約で 2 回目が E-013。変更・パスワード設定は同じ内容の再送が冪等（結果が変わらない）。</t>
+          <t>BCrypt でハッシュ化して保存。平文は DTO 内のみで、ログ・応答に出さない。12〜72文字の ASCII（BCrypt の72バイト上限を超えない）で、半角の英字と数字を各 1 文字以上含める（本人が変更する場合と同じ方針）。応答に password_hash を含めない。管理者が設定したパスワードは暫定扱い（must_change_password=TRUE）で、本人が変更するまで他の API は使えない（E-019）。</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="10" t="n"/>
     </row>
-    <row r="27" ht="34" customHeight="1">
+    <row r="27" ht="49" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>タイムゾーン</t>
+          <t>トークンの失効</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>hire_date は日付のみ（タイムゾーンなし）。created_at は DB の DEFAULT（JST で運用）。updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で更新時に自動更新される。</t>
+          <t>パスワード設定で users.password_changed_at を更新するため、それ以前に発行された JWT（本人が別端末で使っているものを含む）は 401 / E-001 になる。ActiveUserFilter は iat と password_changed_at を比較する。有効期間は 2 時間。ユーザーを INACTIVE にした場合も同じフィルタで即時に拒否する。</t>
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
@@ -1316,47 +1340,93 @@
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>既知の制約</t>
+          <t>排他制御</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限2時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更のサーバー側実施（画面側は ONL-023 で実装済み）・承認待ち申請の承認者付け替え。</t>
+          <t>変更・パスワード設定は SELECT ... FOR UPDATE で対象行を直列化（最後の更新が勝つ。楽観ロック用の列は無い）。メール重複は事前確認＋DB の UNIQUE 制約で二重に防ぎ、同時登録の競合は E-013 に変換する。</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="10" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="19" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>二重実行</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>①API-014 に ⑤パスワード設定（PUT /{id}/password）を追加 ②無効化は PUT の status=INACTIVE ③一覧はページングなし ④メール重複は E-005 ではなくE-013（E-005 の文言は申請期間の重複用のため）⑤E-014/E-015/E-016 を KF-BD-006 に追加 ⑥ADMIN も上長に指定可。</t>
+          <t>登録の二重送信（ボタン連打）は UNIQUE 制約で 2 回目が E-013。変更・パスワード設定は同じ内容の再送が冪等（結果が変わらない）。</t>
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="10" t="n"/>
     </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>タイムゾーン</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>hire_date は日付のみ（タイムゾーンなし）。created_at は DB の DEFAULT（JST で運用）。updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で更新時に自動更新される。</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>ロール変更は発行済み JWT の role claim に即時反映されない（有効期限 2 時間まで。承認系は DB を再確認する）。無効化（INACTIVE）とパスワード設定は ActiveUserFilter により発行済みトークンが即時に拒否される（401 / E-001）。承認待ち申請の承認者の付け替え機能は無い。</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>①API-014 に ⑤パスワード設定（PUT /{id}/password）を追加 ②無効化は PUT の status=INACTIVE ③一覧はページングなし ④メール重複は E-005 ではなくE-013（E-005 の文言は申請期間の重複用のため）⑤E-014/E-015/E-016 を KF-BD-006 に追加 ⑥ADMIN も上長に指定可。</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1369,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E41"/>
+  <dimension ref="A2:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1590,136 +1660,136 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="11" ht="49" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>create：初期パスワードを登録</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>saveAndFlush に渡る User の mustChangePassword が true。passwordHash は encode の結果</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="49" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>create：英字のみ／数字のみの 12 文字パスワード（DTO 検証は通過）</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>E-002 / 400「新しいパスワードは半角の英字と数字を両方含めてください。」。save は呼ばれない</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>checkPolicy の確認。メール重複・所属・上長の検証の後に判定される</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="49" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>create：UTF-8 で 72 バイトを超える値を Service に直接渡す</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>E-002 / 400「新しいパスワードが長すぎます（半角で72文字以内にしてください）。」</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>9.2 UserService#update / resetPassword（Mockito）</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>他人の氏名・ロール・所属・上長を変更</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>値が置き換わり saveAndFlush が 1 回。password_hash は変わらない</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>他人（部下なし）を INACTIVE にする／INACTIVE→ACTIVE に戻す</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>status が更新される。物理削除は行われない</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>再有効化時は上長が ACTIVE であること</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>存在しない id</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>E-015 / 404</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>自分自身を INACTIVE にする</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>E-010 / 403。更新されない</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -1732,22 +1802,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>自分自身のロールを MANAGER に変更</t>
+          <t>他人（部下なし）を INACTIVE にする／INACTIVE→ACTIVE に戻す</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>E-010 / 403</t>
+          <t>status が更新される。物理削除は行われない</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>ADMIN のまま氏名だけ変更するのは成功</t>
+          <t>再有効化時は上長が ACTIVE であること</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1834,17 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>managerId に自分自身を指定</t>
+          <t>存在しない id</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>E-014 / 400</t>
+          <t>E-015 / 404</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
     </row>
-    <row r="20" ht="49" customHeight="1">
+    <row r="20" ht="19" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>14</t>
@@ -1787,19 +1857,15 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>循環: C の上長=B、B の上長=A のとき A の上長を C に変更</t>
+          <t>自分自身を INACTIVE にする</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>E-014 / 400。warn ログ</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>A→C→B→A の循環。depth 上限 100 超過でも E-014</t>
-        </is>
-      </c>
+          <t>E-010 / 403。更新されない</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1814,17 +1880,21 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>有効な部下がいる MANAGER を INACTIVE／EMPLOYEE に変更</t>
+          <t>自分自身のロールを MANAGER に変更</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>E-016 / 409。部下がすべて INACTIVE なら成功</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
+          <t>E-010 / 403</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ADMIN のまま氏名だけ変更するのは成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>16</t>
@@ -1832,24 +1902,20 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>境界</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>メールアドレスを自分自身の現在値のまま更新</t>
+          <t>managerId に自分自身を指定</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>重複とみなされず成功</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>existsByEmailAndIdNot(自分除く)</t>
-        </is>
-      </c>
+          <t>E-014 / 400</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="49" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1859,121 +1925,152 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>循環: C の上長=B、B の上長=A のとき A の上長を C に変更</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>E-014 / 400。warn ログ</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>A→C→B→A の循環。depth 上限 100 超過でも E-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>有効な部下がいる MANAGER を INACTIVE／EMPLOYEE に変更</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>E-016 / 409。部下がすべて INACTIVE なら成功</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>メールアドレスを自分自身の現在値のまま更新</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>重複とみなされず成功</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>existsByEmailAndIdNot(自分除く)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="49" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>resetPassword: 新パスワードを設定</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>passwordHash が encode(新) に変わり、旧ハッシュと異なる。存在しない id は E-015</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>ログにパスワードが出ない</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>9.3 AdminUserController（MockMvc / 結合）</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="49" customHeight="1">
+    <row r="27" ht="79" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>resetPassword：新パスワード（12文字以上・英数字）</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>passwordHash が encode(新) に変わり、mustChangePassword=true、passwordChangedAt が現在日時（Asia/Tokyo）、failedLoginCount=0、lockedUntil=null。saveAndFlush 1 回</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>EMPLOYEE / MANAGER が 5 操作それぞれを呼ぶ</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>すべて 403 E-010</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>handleAccessDenied が効いていること（500 にならない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>GET 一覧: keyword に氏名の一部・メールの一部（大文字小文字違い）</t>
+          <t>resetPassword：11文字／英字のみのパスワード</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>部分一致で絞り込まれ id 昇順。password_hash が JSON に含まれない</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>role / status / departmentId の組合せも確認</t>
-        </is>
-      </c>
+          <t>E-002 / 400（「新しいパスワードは12文字以上で入力してください。」／英字と数字の両方を含める旨）。password_hash は更新されない</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1983,12 +2080,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>keyword に % や _ を含む／100文字・101文字</t>
+          <t>resetPassword：ロック中（lockedUntil が未来・failedLoginCount=5）のユーザー</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>% _ はリテラル扱い。100文字は成功、101文字は E-002</t>
+          <t>lockedUntil=null、failedLoginCount=0 になる（ロック解除）</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
@@ -1996,199 +2093,195 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>resetPassword：存在しない id で方針違反のパスワード</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>E-015 / 404（対象取得が方針検査より先）</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>9.3 AdminUserController（MockMvc / 結合）</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="49" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>EMPLOYEE / MANAGER が 5 操作それぞれを呼ぶ</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>すべて 403 E-010</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>handleAccessDenied が効いていること（500 にならない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>GET 一覧: keyword に氏名の一部・メールの一部（大文字小文字違い）</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>部分一致で絞り込まれ id 昇順。password_hash が JSON に含まれない</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>role / status / departmentId の組合せも確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
           <t>境界</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>keyword に % や _ を含む／100文字・101文字</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>% _ はリテラル扱い。100文字は成功、101文字は E-002</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>name 100文字・101文字、email 255文字・256文字</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>100/255 は成功、101/256 は E-002</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="79" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>境界</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>initialPassword 7文字・8文字・72文字・73文字・全角文字</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>7/73/全角は E-002、8/72 は成功</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>initialPassword 11文字・12文字・72文字・73文字・全角文字・英字のみ（12文字以上）・数字のみ（12文字以上）</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>11/73/全角は E-002（@Size／@Pattern のメッセージ）、英字のみ・数字のみは E-002「新しいパスワードは半角の英字と数字を両方含めてください。」、12/72（英数字混在）は成功</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>newPassword も同じ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>role="BOSS"、hireDate 未指定、本文が空／JSON 不正</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>400 E-002（項目別メッセージ／入力内容が正しくありません。）</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>GET ?departmentId=abc、PUT /abc</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>400 E-002（500 にならない）</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>handleTypeMismatch</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>同一メールで POST を 2 スレッド同時実行（結合）</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>一方は 201、他方は 409 E-013。users に 1 行だけ</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE 制約と競合変換の確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>9.4 D6 追加観点（メール正規化）</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="10" t="n"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>email=" Taro@Example.COM " で登録</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>users.email に "taro@example.com" が保存される。応答の email も小文字</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>EmailNormalizer#normalize</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2198,51 +2291,47 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>既存 taro@example.com に対し " TARO@example.com " で登録／変更</t>
+          <t>role="BOSS"、hireDate 未指定、本文が空／JSON 不正</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>E-013 / 409（正規化後に重複）</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>existsByEmail に "taro@example.com" が渡る</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="34" customHeight="1">
+          <t>400 E-002（項目別メッセージ／入力内容が正しくありません。）</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="19" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>GET 一覧 keyword=" TARO " ／ "Example"</t>
+          <t>GET ?departmentId=abc、PUT /abc</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>氏名・メールの部分一致（大文字小文字無視）で絞り込まれる</t>
+          <t>400 E-002（500 にならない）</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>kw は正規化（trim＋小文字）して検索</t>
+          <t>handleTypeMismatch</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2252,15 +2341,257 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
+          <t>同一メールで POST を 2 スレッド同時実行（結合）</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>一方は 201、他方は 409 E-013。users に 1 行だけ</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE 制約と競合変換の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>パスワード設定後、設定前に発行したトークンで GET /api/admin/users（結合）</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>401 / E-001「認証が必要です。再度ログインしてください。」</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>自分自身のパスワードを設定した場合も同様</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>登録した暫定パスワードでログイン → 他の API（GET /api/attendance/monthly など）を呼出し（結合）</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>403 / E-019「初期パスワードのままです。先にパスワードを変更してください。」。PUT /api/auth/password は成功し、以後は通常どおり</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>INACTIVE にしたユーザーの発行済みトークンで API を呼出し（結合）</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>401 / E-001（ActiveUserFilter）</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="49" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>initialPassword／newPassword に先頭・末尾が空白、または空白を含む値</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>E-002「…は半角英数字・記号で入力してください。」（ASCII 0x21〜0x7E のみ許可）</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>9.4 D6 追加観点（メール正規化）</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>email=" Taro@Example.COM " で登録</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>users.email に "taro@example.com" が保存される。応答の email も小文字</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>EmailNormalizer#normalize</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>既存 taro@example.com に対し " TARO@example.com " で登録／変更</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>E-013 / 409（正規化後に重複）</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>existsByEmail に "taro@example.com" が渡る</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>GET 一覧 keyword=" TARO " ／ "Example"</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>氏名・メールの部分一致（大文字小文字無視）で絞り込まれる</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>kw は正規化（trim＋小文字）して検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
           <t>ONL-001 のログインで "Taro@Example.com" と入力</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>登録時に正規化した小文字のメールで認証できる（200）</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>保存時・検索時で同一の正規化</t>
         </is>
@@ -2269,9 +2600,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A47:E47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2284,7 +2615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2370,6 +2701,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="154" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>パスワード方針の変更に対応：初期パスワード・再設定パスワードを 12〜72 文字（英字と数字を各 1 文字以上）に変更し、UserService#checkPolicy（AuthService#validatePolicy）による E-002 のメッセージを追記。登録は must_change_password=TRUE、パスワード設定は must_change_password=TRUE・password_changed_at=現在日時（以前のトークンを無効化）・failed_login_count=0・locked_until=NULL を更新する処理に修正（「強制変更は未実装」「トークン失効は今後対応」の記述を撤回）。mapping / SQL / エラー（E-001 / E-019 を追加）/ テスト観点 / 既知の制約を更新。JWT 有効期間を 2 時間に統一。所属ドロップダウンの取得元 ONL-026 を参照に追加</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2383,7 +2737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F44"/>
+  <dimension ref="A2:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2487,7 +2841,7 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>起動契機</t>
@@ -2495,7 +2849,8 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>画面 SCR-302 の検索ボタン（①）／一覧の行選択（②）／保存ボタン（③登録・④変更）／無効化ボタン（④ status=INACTIVE）／パスワード再設定（⑤）</t>
+          <t>画面 SCR-302 の検索ボタン（①）／一覧の行選択（②）／保存ボタン（③登録・④変更）／無効化ボタン（④ status=INACTIVE）／パスワード再設定（⑤）
+（登録・変更ダイアログの所属ドロップダウンは GET /api/departments＝ONL-026 で取得する）</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -2519,7 +2874,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>事後条件</t>
@@ -2527,7 +2882,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>登録: users に 1 行追加（status=ACTIVE、パスワードは BCrypt ハッシュ）。変更・無効化: users の 1 行を更新。パスワード設定: password_hash のみ更新。いずれも物理削除は行わない。</t>
+          <t>登録: users に 1 行追加（status=ACTIVE、パスワードは BCrypt ハッシュ、must_change_password=TRUE）。変更・無効化: users の 1 行を更新。パスワード設定: password_hash を更新し、must_change_password=TRUE（本人が初回ログイン後に変更するまで暫定）、password_changed_at=現在日時（JST。これより前に発行された JWT は無効化され 401 / E-001 になる）、failed_login_count=0、locked_until=NULL（アカウントロックも解除）にする。いずれも物理削除は行わない。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -2632,7 +2987,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>E-002 / E-010 / E-012</t>
+          <t>E-001 / E-002 / E-010 / E-012 / E-013〜E-016 / E-019</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -2692,7 +3047,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>パスワード BCrypt・8文字以上、個人情報はログでマスク</t>
+          <t>パスワード BCrypt・12文字以上（英字と数字を含む）、個人情報はログでマスク</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -2819,426 +3174,390 @@
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>ONL-001</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>AuthService#validatePolicy（パスワード方針の定義元）、ActiveUserFilter（パスワード変更後・無効化後のトークン拒否）、PasswordChangeRequiredFilter（暫定パスワードのままの操作を E-019 / 403 で拒否）</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>本処理で設定した暫定パスワードを本人が変更する処理（must_change_password=FALSE に戻す）</t>
+        </is>
+      </c>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="10" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>ONL-026</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>部署一覧取得</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>登録・変更画面（SCR-302）の所属ドロップダウン用 GET /api/departments</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>controller</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>AdminUserController</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>API-014 の 5 操作の受付・ログインユーザーID の取り出し</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>controller/AdminUserController.java</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>UserService</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>ユーザー管理の業務ロジック（検索・登録・変更・パスワード設定、上長・循環・自己保護チェック）</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>service/UserService.java</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="64" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>repository</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>UserRepository</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>検索・メール重複（existsByEmail / existsByEmailAndIdNot）・行ロック・部下有無のメソッドを追加</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>repository/UserRepository.java</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-001）＋メソッド追加</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
+          <t>controller</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>AdminUserController</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>API-014 の 5 操作の受付・ログインユーザーID の取り出し</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>controller/AdminUserController.java</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>UserService</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー管理の業務ロジック（検索・登録・変更・パスワード設定、上長・循環・自己保護チェック）</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>service/UserService.java</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>repository</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>UserRepository</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>検索・メール重複（existsByEmail / existsByEmailAndIdNot）・行ロック・部下有無のメソッドを追加</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>repository/UserRepository.java</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-001）＋メソッド追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>repository</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>DepartmentRepository</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>部署の存在確認・名称取得</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>repository/DepartmentRepository.java</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-007 で定義）＋追加</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>users テーブルのマッピング</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>entity/User.java</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>departments テーブルのマッピング</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>entity/Department.java</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-007 で定義）＋追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>dto</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>UserCreateRequest</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>DTO(record)</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>登録リクエスト＋入力チェック</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>dto/UserCreateRequest.java</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>dto</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>UserUpdateRequest</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>DTO(record)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>変更・無効化リクエスト＋入力チェック</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>dto/UserUpdateRequest.java</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
         </is>
       </c>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>departments テーブルのマッピング</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>entity/Department.java</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-007 で定義）＋追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
           <t>dto</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>UserCreateRequest</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>登録リクエスト＋入力チェック</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>dto/UserCreateRequest.java</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>UserUpdateRequest</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>変更・無効化リクエスト＋入力チェック</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>dto/UserUpdateRequest.java</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>PasswordResetRequest</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>パスワード設定リクエスト＋入力チェック</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>dto/PasswordResetRequest.java</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>dto</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>UserResponse</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>DTO(record)</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>ユーザー1件の表現（password_hash は含めない）</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>dto/UserResponse.java</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>dto</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>UserListResponse</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>DTO(record)</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>一覧応答 {users[], total}</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>dto/UserListResponse.java</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>dto</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>UserDetailResponse</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>DTO(record)</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>単一応答 {user}</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>dto/UserDetailResponse.java</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3250,107 +3569,204 @@
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>UserResponse</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー1件の表現（password_hash は含めない）</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>dto/UserResponse.java</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>UserListResponse</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>一覧応答 {users[], total}</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>dto/UserListResponse.java</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>UserDetailResponse</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>単一応答 {user}</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>dto/UserDetailResponse.java</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>SecurityConfig</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>@EnableMethodSecurity は ONL-001 で定義済み（変更なし）</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>config/SecurityConfig.java</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="49" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="46" ht="49" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>ControllerAdvice</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>handleAccessDenied / handleTypeMismatch は ONL-001 で定義済み（変更なし）</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>exception/GlobalExceptionHandler.java</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001）</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>BusinessException</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>業務エラー（E-010 / E-013〜E-016 の送出）</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>exception/BusinessException.java</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="28">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="B12:F12"/>
@@ -3359,10 +3775,11 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="B9:F9"/>
@@ -3370,6 +3787,7 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3595,7 +4013,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="94" customHeight="1">
+    <row r="7" ht="199" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>initialPassword</t>
@@ -3618,14 +4036,15 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>8〜72文字、半角英数字・記号（ASCII 0x21〜0x7E、空白不可）</t>
+          <t>12〜72文字、半角英数字・記号（ASCII 0x21〜0x7E、空白不可）。英字と数字を各 1 文字以上含む</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>@NotBlank → E-002「初期パスワードは必須入力です。」
-@Size(min=8,max=72) → E-002「初期パスワードは8文字以上72文字以内で入力してください。」
-@Pattern(^[\x21-\x7E]*$) → E-002「初期パスワードは半角英数字・記号で入力してください。」</t>
+@Size(min=12,max=72) → E-002「初期パスワードは12文字以上72文字以内で入力してください。」
+@Pattern(^[\x21-\x7E]*$) → E-002「初期パスワードは半角英数字・記号で入力してください。」
+パスワード方針（UserService#checkPolicy → AuthService#validatePolicy）→ E-002「新しいパスワードは半角の英字と数字を両方含めてください。」（英字のみ・数字のみ）／「新しいパスワードは12文字以上で入力してください。」／「新しいパスワードが長すぎます（半角で72文字以内にしてください）。」（UTF-8 で 72 バイト超）</t>
         </is>
       </c>
     </row>
@@ -3883,7 +4302,7 @@
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
-    <row r="17" ht="94" customHeight="1">
+    <row r="17" ht="139" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>newPassword</t>
@@ -3906,14 +4325,15 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>8〜72文字、半角英数字・記号（登録時の initialPassword と同じ規則）</t>
+          <t>12〜72文字、半角英数字・記号（登録時の initialPassword と同じ規則）。英字と数字を各 1 文字以上含む</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>@NotBlank → E-002「新しいパスワードは必須入力です。」
-@Size(min=8,max=72) → E-002「新しいパスワードは8文字以上72文字以内で入力してください。」
-@Pattern → E-002「新しいパスワードは半角英数字・記号で入力してください。」</t>
+@Size(min=12,max=72) → E-002「新しいパスワードは12文字以上72文字以内で入力してください。」
+@Pattern → E-002「新しいパスワードは半角英数字・記号で入力してください。」
+パスワード方針違反 → E-002（登録と同じ 3 種のメッセージ）。現在のパスワードとの比較は行わない（管理者操作）</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5432,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="49" customHeight="1">
+    <row r="12" ht="94" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>⑨</t>
@@ -5020,24 +5440,24 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>パスワードを BCrypt でハッシュ化
-（登録のみ）</t>
+          <t>パスワードは方針を満たすか？
+（登録・パスワード設定）</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>passwordEncoder.encode(initialPassword)。平文は保持・ログ出力しない</t>
+          <t>UserService#checkPolicy → AuthService.validatePolicy(password, null)：12文字以上／UTF-8 で 72 バイト以内／半角の英字と数字を各 1 文字以上。違反は E-002 のメッセージで返す。登録は ⑦ の後、パスワード設定は対象取得（③）の後に行う（⑤〜⑧ は登録・変更のみ）</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>処理</t>
+          <t>判定（No → E-002 を返却  HTTP 400）</t>
         </is>
       </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="79" customHeight="1">
+    <row r="13" ht="154" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑩</t>
@@ -5050,8 +5470,9 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>【登録】新規 User（status=ACTIVE）を saveAndFlush
-【変更】取得済み Entity の項目を置き換えて saveAndFlush
+          <t>【登録】新規 User（status=ACTIVE、password_hash＝BCrypt(initialPassword)、must_change_password=TRUE）を saveAndFlush
+【変更】取得済み Entity の項目を置き換えて saveAndFlush（password_hash は変更しない）
+【パスワード設定】password_hash＝BCrypt(newPassword)、must_change_password=TRUE、password_changed_at＝now(Asia/Tokyo)、failed_login_count=0、locked_until=NULL を saveAndFlush
 メール一意制約違反（競合）は E-013 に変換</t>
         </is>
       </c>
@@ -5128,7 +5549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F220"/>
+  <dimension ref="A2:F233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6176,7 +6597,7 @@
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="10" t="n"/>
     </row>
-    <row r="66" ht="19" customHeight="1">
+    <row r="66" ht="34" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
           <t>説明</t>
@@ -6184,7 +6605,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>重複・所属・上長を検証し、初期パスワードをハッシュ化して users に 1 行追加する。</t>
+          <t>重複・所属・上長・パスワード方針を検証し、初期パスワードをハッシュ化して users に 1 行追加する（初回ログイン時にパスワード変更を強制する暫定パスワードとして登録）。</t>
         </is>
       </c>
       <c r="C66" s="9" t="n"/>
@@ -6292,7 +6713,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>BusinessException(E-013 重複 / E-014 所属・上長不正)</t>
+          <t>BusinessException(E-013 重複 / E-014 所属・上長不正 / E-002 パスワード方針違反)</t>
         </is>
       </c>
       <c r="C72" s="9" t="n"/>
@@ -6300,7 +6721,7 @@
       <c r="E72" s="9" t="n"/>
       <c r="F72" s="10" t="n"/>
     </row>
-    <row r="73" ht="334" customHeight="1">
+    <row r="73" ht="364" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -6315,13 +6736,15 @@
 validateManager(null, req.managerId());                                  // ⑦ 新規は循環なし（targetId = null）
 User u = new User();
 u.setEmail(email);
-u.setPasswordHash(passwordEncoder.encode(req.initialPassword()));        // ⑨ BCrypt
+checkPolicy(req.initialPassword());                                      // ⑨ 12文字以上・英字と数字（違反は E-002 / 400）
+u.setPasswordHash(passwordEncoder.encode(req.initialPassword()));        // ⑩ BCrypt
 u.setName(req.name().strip());
 u.setRole(req.role());
 u.setDepartmentId(req.departmentId());
 u.setManagerId(req.managerId());
 u.setHireDate(req.hireDate());
 u.setStatus("ACTIVE");                                                   // 登録時は常に ACTIVE
+u.setMustChangePassword(true);                                           // 初期パスワードは初回ログイン時に変更を強制する
 try {
     u = userRepository.saveAndFlush(u);                                  // ⑩ INSERT。flush で一意制約を即検査
 } catch (DataIntegrityViolationException e) {
@@ -6352,7 +6775,7 @@
       <c r="E74" s="9" t="n"/>
       <c r="F74" s="10" t="n"/>
     </row>
-    <row r="75" ht="94" customHeight="1">
+    <row r="75" ht="154" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -6362,7 +6785,8 @@
         <is>
           <t>duplicated(item) = new BusinessException("E-013", item + "は既に登録されています。", HttpStatus.CONFLICT)。
 事前確認(exists)は通常ケースの利便のため、最終的な保証は DB の UNIQUE 制約。DataIntegrityViolationException は他の制約違反も含むが、事前検証済みのためメール重複とみなす。
-初期パスワードの強制変更（初回ログイン時）は MVP では実装しない（users にフラグ列が無い）。管理者が本人へ安全に連絡すること。
+初期パスワードは must_change_password=TRUE で登録する。本人がログインすると JWT に claim mcp=true が付き、PasswordChangeRequiredFilter が PUT /api/auth/password 以外の API を E-019「初期パスワードのままです。先にパスワードを変更してください。」（403）で拒否する。パスワード変更（ONL-023）で FALSE に戻る。管理者は初期パスワードを本人へ安全な手段で伝えること。
+方針検査 checkPolicy は ① Bean Validation（@Size / @Pattern）の後に、Service で実施する。重複・所属・上長の検証（⑤〜⑦）の後なので、同時に複数の不備があるとき先に返るのはメール重複・所属・上長のエラー。
 email は trim＋toLowerCase(Locale.ROOT) で正規化して保存する（ONL-001 のログインも同じ正規化で検索するため、大文字小文字の違いでログインできない・二重登録される事故が起きない）。正規化後の値で uq_users_1 が効く。</t>
         </is>
       </c>
@@ -6617,7 +7041,7 @@
       <c r="E89" s="9" t="n"/>
       <c r="F89" s="10" t="n"/>
     </row>
-    <row r="90" ht="124" customHeight="1">
+    <row r="90" ht="139" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -6628,7 +7052,7 @@
           <t>④により、操作者（ADMIN）は自分自身を無効化・降格できない。したがって有効な ADMIN は常に 1 人以上残る（最後の管理者が消える事故の防止）。他の ADMIN の降格・無効化は許可。
 ⑧は「承認者になれるユーザーに部下が残ったまま承認権限を失わせない」ためのチェック。部下の上長を先に付け替えること。無効化済みの部下は数えない。
 再有効化（INACTIVE→ACTIVE）は通常の更新として行う。上長が INACTIVE なら ⑦ で E-014。
-既知の制約: 無効化したユーザーが承認者として残っている承認待ち申請の付け替え機能は無い（運用で先に処理する）。無効化しても発行済み JWT は有効期限（8時間）まで使える。ロール変更も次回ログインまで反映されない。
+既知の制約: 無効化したユーザーが承認者として残っている承認待ち申請の付け替え機能は無い（運用で先に処理する）。無効化したユーザー（INACTIVE）の発行済み JWT は、ActiveUserFilter が毎回 users を確認して 401 / E-001 で拒否するため即時に使えなくなる。ロール変更は JWT の role claim が有効期限（2 時間）まで古いままだが、承認系は DB の role を再確認する（ONL-010）。
 入社日の変更は以後の BAT-001 付与にのみ影響し、付与済みの休暇は再計算しない。</t>
         </is>
       </c>
@@ -6682,7 +7106,7 @@
       <c r="E94" s="9" t="n"/>
       <c r="F94" s="10" t="n"/>
     </row>
-    <row r="95" ht="19" customHeight="1">
+    <row r="95" ht="34" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
           <t>説明</t>
@@ -6690,7 +7114,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーの password_hash を新しいパスワードの BCrypt ハッシュに置き換える（初期化・再設定共通）。</t>
+          <t>対象ユーザーの password_hash を新しいパスワード（12文字以上の方針を満たすもの）の BCrypt ハッシュに置き換える（初期化・再設定共通）。再設定後は暫定パスワード扱いとなり、以前に発行されたトークンは無効になり、アカウントロックも解除される。</t>
         </is>
       </c>
       <c r="C95" s="9" t="n"/>
@@ -6818,7 +7242,7 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>BusinessException("E-015", 404)</t>
+          <t>BusinessException("E-015", 404) / BusinessException("E-002", 400)（パスワード方針違反）</t>
         </is>
       </c>
       <c r="C102" s="9" t="n"/>
@@ -6826,7 +7250,7 @@
       <c r="E102" s="9" t="n"/>
       <c r="F102" s="10" t="n"/>
     </row>
-    <row r="103" ht="79" customHeight="1">
+    <row r="103" ht="154" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -6834,8 +7258,13 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>User u = userRepository.findByIdForUpdate(id).orElseThrow(UserService::notFound);
+          <t>User u = userRepository.findByIdForUpdate(id).orElseThrow(UserService::notFound);   // ③ E-015 404（FOR UPDATE）
+checkPolicy(req.newPassword());                                  // ⑨ 12文字以上・英字と数字・72バイト以内（違反は E-002 / 400）
 u.setPasswordHash(passwordEncoder.encode(req.newPassword()));    // BCrypt。旧パスワードは確認しない（管理者操作）
+u.setMustChangePassword(true);                                   // 管理者が設定したパスワードは本人が変更するまで暫定扱い
+u.setPasswordChangedAt(LocalDateTime.now(ZoneId.of("Asia/Tokyo")));  // これより前に発行されたトークンを失効させる
+u.setFailedLoginCount(0);                                        // ロック解除も兼ねる
+u.setLockedUntil(null);
 userRepository.saveAndFlush(u);
 log.info("User password reset: id={}, actorId={}", id, actorId); // パスワード・ハッシュは出力しない
 return new UserDetailResponse(toResponses(List.of(u)).get(0));</t>
@@ -6854,7 +7283,7 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>UserRepository#findByIdForUpdate / PasswordEncoder#encode</t>
+          <t>UserRepository#findByIdForUpdate / checkPolicy / PasswordEncoder#encode / UserRepository#saveAndFlush</t>
         </is>
       </c>
       <c r="C104" s="9" t="n"/>
@@ -6862,7 +7291,7 @@
       <c r="E104" s="9" t="n"/>
       <c r="F104" s="10" t="n"/>
     </row>
-    <row r="105" ht="34" customHeight="1">
+    <row r="105" ht="109" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -6870,8 +7299,10 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>自分自身のパスワードにも使える。INACTIVE ユーザーも許可（再有効化前の準備）。
-発行済みの JWT は失効しない（トークン失効は今後対応）。</t>
+          <t>自分自身のパスワードにも使える（その場合、現在のトークンも password_changed_at より前の発行なので以後の API は 401 / E-001 になる。再ログインが必要）。INACTIVE ユーザーも許可（再有効化前の準備）。
+トークンの失効：ActiveUserFilter が JWT の発行時刻（iat）と users.password_changed_at を比較し、パスワード変更・再設定より前に発行されたトークンを 401 / E-001「認証が必要です。再度ログインしてください。」で拒否する（ONL-001 で定義）。JWT の有効期間は 2 時間。
+再設定後の本人は、新しいパスワードでログインした後、PasswordChangeRequiredFilter により PUT /api/auth/password（ONL-023）以外を E-019 / 403 で拒否され、パスワード変更を求められる。
+failed_login_count=0・locked_until=NULL により、ログイン失敗の連続でロックされたアカウントの解除を兼ねる。</t>
         </is>
       </c>
       <c r="C105" s="9" t="n"/>
@@ -8514,7 +8945,7 @@
     <row r="208">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>6.15  操作別の処理手順（API-014 の 5 操作）</t>
+          <t>6.15  UserService#checkPolicy</t>
         </is>
       </c>
       <c r="B208" s="9" t="n"/>
@@ -8524,218 +8955,157 @@
       <c r="F208" s="10" t="n"/>
     </row>
     <row r="209" ht="19" customHeight="1">
-      <c r="A209" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>HTTP・パス</t>
-        </is>
-      </c>
-      <c r="C209" s="6" t="inlineStr">
-        <is>
-          <t>Controller → Service</t>
-        </is>
-      </c>
-      <c r="D209" s="6" t="inlineStr">
-        <is>
-          <t>処理手順</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
-        <is>
-          <t>成功時</t>
-        </is>
-      </c>
-      <c r="F209" s="6" t="inlineStr">
-        <is>
-          <t>主なエラー</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="79" customHeight="1">
-      <c r="A210" s="7" t="inlineStr">
-        <is>
-          <t>①一覧</t>
-        </is>
-      </c>
-      <c r="B210" s="7" t="inlineStr">
-        <is>
-          <t>GET /api/admin/users</t>
-        </is>
-      </c>
-      <c r="C210" s="7" t="inlineStr">
-        <is>
-          <t>list → search</t>
-        </is>
-      </c>
-      <c r="D210" s="7" t="inlineStr">
-        <is>
-          <t>keyword/role/status/departmentId を検証 → UserRepository#search → 所属名・上長名を一括取得 → UserListResponse</t>
-        </is>
-      </c>
-      <c r="E210" s="7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F210" s="7" t="inlineStr">
-        <is>
-          <t>E-002, E-010</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="34" customHeight="1">
-      <c r="A211" s="7" t="inlineStr">
-        <is>
-          <t>②詳細</t>
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Service 内部メソッド（パスワード方針）</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="n"/>
+      <c r="D209" s="9" t="n"/>
+      <c r="E209" s="9" t="n"/>
+      <c r="F209" s="10" t="n"/>
+    </row>
+    <row r="210" ht="19" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B210" s="12" t="inlineStr">
+        <is>
+          <t>private static void checkPolicy(String password)</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="n"/>
+      <c r="D210" s="9" t="n"/>
+      <c r="E210" s="9" t="n"/>
+      <c r="F210" s="10" t="n"/>
+    </row>
+    <row r="211" ht="19" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
         <is>
-          <t>GET /api/admin/users/{id}</t>
-        </is>
-      </c>
-      <c r="C211" s="7" t="inlineStr">
-        <is>
-          <t>get → get</t>
-        </is>
-      </c>
-      <c r="D211" s="7" t="inlineStr">
-        <is>
-          <t>findById → UserDetailResponse</t>
-        </is>
-      </c>
-      <c r="E211" s="7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>E-015, E-010</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="49" customHeight="1">
-      <c r="A212" s="7" t="inlineStr">
-        <is>
-          <t>③登録</t>
+          <t>管理者が設定するパスワード（初期パスワード・再設定）にも、本人が変更するときと同じパスワード方針を適用する。</t>
+        </is>
+      </c>
+      <c r="C211" s="9" t="n"/>
+      <c r="D211" s="9" t="n"/>
+      <c r="E211" s="9" t="n"/>
+      <c r="F211" s="10" t="n"/>
+    </row>
+    <row r="212" ht="19" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
         <is>
-          <t>POST /api/admin/users</t>
-        </is>
-      </c>
-      <c r="C212" s="7" t="inlineStr">
-        <is>
-          <t>create → create</t>
-        </is>
-      </c>
-      <c r="D212" s="7" t="inlineStr">
-        <is>
-          <t>メール重複 → 所属 → 上長 → BCrypt → INSERT（status=ACTIVE）→ 応答</t>
-        </is>
-      </c>
-      <c r="E212" s="7" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="F212" s="7" t="inlineStr">
-        <is>
-          <t>E-002, E-013, E-014, E-010</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="109" customHeight="1">
-      <c r="A213" s="7" t="inlineStr">
-        <is>
-          <t>④変更・無効化・再有効化</t>
-        </is>
-      </c>
-      <c r="B213" s="7" t="inlineStr">
-        <is>
-          <t>PUT /api/admin/users/{id}</t>
-        </is>
-      </c>
-      <c r="C213" s="7" t="inlineStr">
-        <is>
-          <t>update → update</t>
-        </is>
-      </c>
-      <c r="D213" s="7" t="inlineStr">
-        <is>
-          <t>行ロック取得 → 自己保護 → メール重複（自分除く）→ 所属 → 上長（循環） → 部下確認 → UPDATE → 応答。無効化は status=INACTIVE（論理削除。物理削除は行わない）</t>
-        </is>
-      </c>
-      <c r="E213" s="7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F213" s="7" t="inlineStr">
-        <is>
-          <t>E-002, E-010, E-013, E-014, E-015, E-016</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="49" customHeight="1">
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C212" s="9" t="n"/>
+      <c r="D212" s="9" t="n"/>
+      <c r="E212" s="9" t="n"/>
+      <c r="F212" s="10" t="n"/>
+    </row>
+    <row r="213" ht="19" customHeight="1">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="n"/>
+      <c r="E213" s="9" t="n"/>
+      <c r="F213" s="10" t="n"/>
+    </row>
+    <row r="214" ht="19" customHeight="1">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>⑤パスワード設定</t>
+          <t>password</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
         <is>
-          <t>PUT /api/admin/users/{id}/password</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>resetPassword → resetPassword</t>
-        </is>
-      </c>
-      <c r="D214" s="7" t="inlineStr">
-        <is>
-          <t>行ロック取得 → BCrypt → password_hash のみ更新 → 応答</t>
-        </is>
-      </c>
-      <c r="E214" s="7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F214" s="7" t="inlineStr">
-        <is>
-          <t>E-002, E-010, E-015</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="8" t="inlineStr">
-        <is>
-          <t>6.16  SecurityConfig の前提（ONL-001「共通基盤への追加改修」で定義済み。本処理では変更しない）</t>
-        </is>
-      </c>
-      <c r="B216" s="9" t="n"/>
+          <t>検査するパスワード（平文。ログに出さない）</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="n"/>
+      <c r="E214" s="9" t="n"/>
+      <c r="F214" s="10" t="n"/>
+    </row>
+    <row r="215" ht="19" customHeight="1">
+      <c r="A215" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="n"/>
+      <c r="D215" s="9" t="n"/>
+      <c r="E215" s="9" t="n"/>
+      <c r="F215" s="10" t="n"/>
+    </row>
+    <row r="216" ht="19" customHeight="1">
+      <c r="A216" s="11" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>BusinessException("E-002", 400)  メッセージは AuthService#validatePolicy の戻り値</t>
+        </is>
+      </c>
       <c r="C216" s="9" t="n"/>
       <c r="D216" s="9" t="n"/>
       <c r="E216" s="9" t="n"/>
       <c r="F216" s="10" t="n"/>
     </row>
-    <row r="217" ht="19" customHeight="1">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>変更</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
+    <row r="217" ht="139" customHeight="1">
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B217" s="12" t="inlineStr">
+        <is>
+          <t>String problem = AuthService.validatePolicy(password, null);   // 現在のパスワードとの比較は行わない（null）
+if (problem != null)
+    throw new BusinessException("E-002", problem, HttpStatus.BAD_REQUEST);
+// AuthService#validatePolicy の判定（定義元は ONL-001／ONL-023。この順で最初の違反だけ返す）
+//  1) password.length() &lt; 12                       → 「新しいパスワードは12文字以上で入力してください。」
+//  2) UTF-8 のバイト数 &gt; 72（BCrypt の上限）          → 「新しいパスワードが長すぎます（半角で72文字以内にしてください）。」
+//  3) 半角の英字(A-Za-z)・数字(0-9)のどちらかが無い    → 「新しいパスワードは半角の英字と数字を両方含めてください。」
+//  4) currentPassword と同一（本処理では null のため判定されない）</t>
         </is>
       </c>
       <c r="C217" s="9" t="n"/>
@@ -8743,15 +9113,15 @@
       <c r="E217" s="9" t="n"/>
       <c r="F217" s="10" t="n"/>
     </row>
-    <row r="218" ht="34" customHeight="1">
-      <c r="A218" s="7" t="inlineStr">
-        <is>
-          <t>@EnableMethodSecurity</t>
+    <row r="218" ht="19" customHeight="1">
+      <c r="A218" s="11" t="inlineStr">
+        <is>
+          <t>呼出先</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>ONL-001 で SecurityConfig に付与済み。Controller の @PreAuthorize が有効。ROLE_ADMIN は JwtAuthenticationConverter（claim "role" → ROLE_&lt;role&gt;）で付与済み</t>
+          <t>AuthService#validatePolicy</t>
         </is>
       </c>
       <c r="C218" s="9" t="n"/>
@@ -8759,15 +9129,16 @@
       <c r="E218" s="9" t="n"/>
       <c r="F218" s="10" t="n"/>
     </row>
-    <row r="219" ht="34" customHeight="1">
-      <c r="A219" s="7" t="inlineStr">
-        <is>
-          <t>例外応答</t>
+    <row r="219" ht="64" customHeight="1">
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>トークン不正・期限切れは AuthenticationEntryPoint（401 / E-001）、フィルタ段階の権限不足は AccessDeniedHandler（403 / E-010）、@PreAuthorize の拒否は handleAccessDenied（403 / E-010）。いずれも JSON の ErrorResponse</t>
+          <t>Bean Validation（@Size(min=12,max=72)・@Pattern(^[\x21-\x7E]*$)）が先に働くため、文字数・文字種の違反は多くの場合 DTO の項目別メッセージ（「初期パスワードは12文字以上72文字以内で入力してください。」など）で返り、英字・数字の両方を含むか（3）だけが Service で検出される。いずれも E-002 / 400。
+最小文字数は AuthService#MIN_PASSWORD_LENGTH（12）。KF-RD-002 §4 のパスワードポリシーに従う。</t>
         </is>
       </c>
       <c r="C219" s="9" t="n"/>
@@ -8775,30 +9146,295 @@
       <c r="E219" s="9" t="n"/>
       <c r="F219" s="10" t="n"/>
     </row>
-    <row r="220" ht="19" customHeight="1">
-      <c r="A220" s="7" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>6.16  操作別の処理手順（API-014 の 5 操作）</t>
+        </is>
+      </c>
+      <c r="B221" s="9" t="n"/>
+      <c r="C221" s="9" t="n"/>
+      <c r="D221" s="9" t="n"/>
+      <c r="E221" s="9" t="n"/>
+      <c r="F221" s="10" t="n"/>
+    </row>
+    <row r="222" ht="19" customHeight="1">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>HTTP・パス</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>Controller → Service</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>処理手順</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>成功時</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>主なエラー</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="79" customHeight="1">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>①一覧</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>GET /api/admin/users</t>
+        </is>
+      </c>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t>list → search</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>keyword/role/status/departmentId を検証 → UserRepository#search → 所属名・上長名を一括取得 → UserListResponse</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>E-002, E-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="34" customHeight="1">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>②詳細</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>GET /api/admin/users/{id}</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t>get → get</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>findById → UserDetailResponse</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>E-015, E-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="94" customHeight="1">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>③登録</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>POST /api/admin/users</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t>create → create</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>メール重複 → 所属 → 上長 → パスワード方針（12文字以上・英字と数字）→ BCrypt → INSERT（status=ACTIVE、must_change_password=TRUE）→ 応答</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>E-002, E-013, E-014, E-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="109" customHeight="1">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>④変更・無効化・再有効化</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>PUT /api/admin/users/{id}</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t>update → update</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>行ロック取得 → 自己保護 → メール重複（自分除く）→ 所属 → 上長（循環） → 部下確認 → UPDATE → 応答。無効化は status=INACTIVE（論理削除。物理削除は行わない）</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>E-002, E-010, E-013, E-014, E-015, E-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="124" customHeight="1">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>⑤パスワード設定</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>PUT /api/admin/users/{id}/password</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
+        <is>
+          <t>resetPassword → resetPassword</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>行ロック取得 → パスワード方針 → BCrypt → password_hash・must_change_password=TRUE・password_changed_at=now・failed_login_count=0・locked_until=NULL を更新 → 応答（以前のトークンは無効）</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>E-002, E-010, E-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>6.17  SecurityConfig の前提（ONL-001「共通基盤への追加改修」で定義済み。本処理では変更しない）</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="n"/>
+      <c r="C229" s="9" t="n"/>
+      <c r="D229" s="9" t="n"/>
+      <c r="E229" s="9" t="n"/>
+      <c r="F229" s="10" t="n"/>
+    </row>
+    <row r="230" ht="19" customHeight="1">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>変更</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="n"/>
+      <c r="D230" s="9" t="n"/>
+      <c r="E230" s="9" t="n"/>
+      <c r="F230" s="10" t="n"/>
+    </row>
+    <row r="231" ht="34" customHeight="1">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>@EnableMethodSecurity</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>ONL-001 で SecurityConfig に付与済み。Controller の @PreAuthorize が有効。ROLE_ADMIN は JwtAuthenticationConverter（claim "role" → ROLE_&lt;role&gt;）で付与済み</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="n"/>
+      <c r="D231" s="9" t="n"/>
+      <c r="E231" s="9" t="n"/>
+      <c r="F231" s="10" t="n"/>
+    </row>
+    <row r="232" ht="34" customHeight="1">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>例外応答</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>トークン不正・期限切れは AuthenticationEntryPoint（401 / E-001）、フィルタ段階の権限不足は AccessDeniedHandler（403 / E-010）、@PreAuthorize の拒否は handleAccessDenied（403 / E-010）。いずれも JSON の ErrorResponse</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="n"/>
+      <c r="D232" s="9" t="n"/>
+      <c r="E232" s="9" t="n"/>
+      <c r="F232" s="10" t="n"/>
+    </row>
+    <row r="233" ht="19" customHeight="1">
+      <c r="A233" s="7" t="inlineStr">
         <is>
           <t>URL ルール</t>
         </is>
       </c>
-      <c r="B220" s="7" t="inlineStr">
+      <c r="B233" s="7" t="inlineStr">
         <is>
           <t>変更なし（ログイン API 以外は authenticated）。ロール判定は URL ではなく @PreAuthorize で行う</t>
         </is>
       </c>
-      <c r="C220" s="9" t="n"/>
-      <c r="D220" s="9" t="n"/>
-      <c r="E220" s="9" t="n"/>
-      <c r="F220" s="10" t="n"/>
+      <c r="C233" s="9" t="n"/>
+      <c r="D233" s="9" t="n"/>
+      <c r="E233" s="9" t="n"/>
+      <c r="F233" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="210">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="C144:F144"/>
     <mergeCell ref="C159:F159"/>
+    <mergeCell ref="B209:F209"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="A50:F50"/>
@@ -8809,6 +9445,7 @@
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B180:F180"/>
     <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B231:F231"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="B179:F179"/>
@@ -8822,6 +9459,7 @@
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="B168:F168"/>
+    <mergeCell ref="B230:F230"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="B118:F118"/>
@@ -8834,9 +9472,12 @@
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B133:F133"/>
     <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C214:F214"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B94:F94"/>
     <mergeCell ref="C27:F27"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="A221:F221"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B72:F72"/>
@@ -8851,6 +9492,7 @@
     <mergeCell ref="B219:F219"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="C69:F69"/>
+    <mergeCell ref="B210:F210"/>
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="C83:F83"/>
     <mergeCell ref="B120:F120"/>
@@ -8870,13 +9512,13 @@
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B187:F187"/>
     <mergeCell ref="C40:F40"/>
-    <mergeCell ref="A216:F216"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="C201:F201"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B189:F189"/>
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B216:F216"/>
     <mergeCell ref="B198:F198"/>
     <mergeCell ref="B188:F188"/>
     <mergeCell ref="B4:F4"/>
@@ -8887,6 +9529,7 @@
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="B218:F218"/>
+    <mergeCell ref="B232:F232"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="C82:F82"/>
@@ -8896,6 +9539,7 @@
     <mergeCell ref="C174:F174"/>
     <mergeCell ref="B190:F190"/>
     <mergeCell ref="B202:F202"/>
+    <mergeCell ref="B215:F215"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="B48:F48"/>
@@ -8918,6 +9562,7 @@
     <mergeCell ref="B147:F147"/>
     <mergeCell ref="B178:F178"/>
     <mergeCell ref="C113:F113"/>
+    <mergeCell ref="A229:F229"/>
     <mergeCell ref="C143:F143"/>
     <mergeCell ref="C100:F100"/>
     <mergeCell ref="C112:F112"/>
@@ -8940,6 +9585,7 @@
     <mergeCell ref="B154:F154"/>
     <mergeCell ref="B206:F206"/>
     <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B212:F212"/>
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B203:F203"/>
     <mergeCell ref="B138:F138"/>
@@ -8952,7 +9598,6 @@
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B93:F93"/>
     <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B220:F220"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B86:F86"/>
@@ -8976,6 +9621,7 @@
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="C55:F55"/>
     <mergeCell ref="C99:F99"/>
+    <mergeCell ref="B211:F211"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B95:F95"/>
@@ -8987,6 +9633,7 @@
     <mergeCell ref="C115:F115"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C213:F213"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B197:F197"/>
     <mergeCell ref="B153:F153"/>
@@ -9003,7 +9650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F35"/>
+  <dimension ref="A2:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9354,261 +10001,389 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
+    <row r="14" ht="49" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>must_change_password</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>mustChangePassword</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>C TRUE（登録）／U TRUE（パスワード設定）</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>既定 FALSE。TRUE の間は PUT /api/auth/password 以外の API を E-019 で拒否（本人が変更すると FALSE）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>password_changed_at</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>passwordChangedAt</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>U 現在日時（パスワード設定）</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>JST。これより前に発行された JWT は ActiveUserFilter が 401 / E-001 にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>failed_login_count</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>failedLoginCount</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>U 0（パスワード設定）</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>連続ログイン失敗回数。既定 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>locked_until</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>lockedUntil</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>U NULL（パスワード設定）</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>ロック解除時刻。NULL＝ロックなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>■ departments</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>○ 存在確認</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>○ 所属名の出力</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="64" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_departments_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="94" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="94" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>一覧（UserRepository#search）</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users
  WHERE (LOWER(name) LIKE LOWER('%'||?||'%') ESCAPE '\' OR LOWER(email) LIKE LOWER('%'||?||'%') ESCAPE '\')
@@ -9618,71 +10393,6 @@
 SELECT * FROM users WHERE id IN (?, ...)      -- 上長名</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>対象の行ロック取得（findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>メール重複確認</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>SELECT 1 FROM users WHERE email = ? [AND id &lt;&gt; ?] LIMIT 1   -- ? は EmailNormalizer#normalize 済み（小文字）</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>所属・上長の確認</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM departments WHERE id = ?
-SELECT * FROM users WHERE id = ?          -- 上長。循環確認で上長の上長…を繰り返し取得</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>部下の有無</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>SELECT 1 FROM users WHERE manager_id = ? AND status = 'ACTIVE' LIMIT 1</t>
-        </is>
-      </c>
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
@@ -9691,13 +10401,12 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>登録（saveAndFlush）</t>
+          <t>対象の行ロック取得（findByIdForUpdate）</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO users(email, password_hash, name, role, department_id, manager_id, hire_date, status)
-VALUES (?, ?, ?, ?, ?, ?, ?, 'ACTIVE')     -- created_at / updated_at は DB の DEFAULT</t>
+          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
@@ -9705,16 +10414,15 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="30" ht="64" customHeight="1">
+    <row r="30" ht="19" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>変更・無効化・パスワード設定（saveAndFlush）</t>
+          <t>メール重複確認</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>UPDATE users SET email=?, password_hash=?, name=?, role=?, department_id=?, manager_id=?, hire_date=?, status=? WHERE id=?
-※Hibernate は既定で全更新対象列を更新する（password_hash は取得時の値のまま）。@DynamicUpdate は不要。updated_at は SET に含めず DB トリガ trg_users_updated_at で自動更新</t>
+          <t>SELECT 1 FROM users WHERE email = ? [AND id &lt;&gt; ?] LIMIT 1   -- ? は EmailNormalizer#normalize 済み（小文字）</t>
         </is>
       </c>
       <c r="C30" s="9" t="n"/>
@@ -9722,110 +10430,196 @@
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="10" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>7.3 設定値</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n"/>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>所属・上長の確認</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM departments WHERE id = ?
+SELECT * FROM users WHERE id = ?          -- 上長。循環確認で上長の上長…を繰り返し取得</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>部下の有無</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>SELECT 1 FROM users WHERE manager_id = ? AND status = 'ACTIVE' LIMIT 1</t>
+        </is>
+      </c>
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33" ht="49" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>登録（saveAndFlush）</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO users(email, password_hash, name, role, department_id, manager_id, hire_date, status, must_change_password)
+VALUES (?, ?, ?, ?, ?, ?, ?, 'ACTIVE', TRUE)     -- created_at / updated_at / failed_login_count は DB の DEFAULT</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>変更・無効化（saveAndFlush）</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>UPDATE users SET email=?, password_hash=?, name=?, role=?, department_id=?, manager_id=?, hire_date=?, status=? WHERE id=?
+※Hibernate は既定で全更新対象列を更新する（password_hash は取得時の値のまま）。@DynamicUpdate は不要。updated_at は SET に含めず DB トリガ trg_users_updated_at で自動更新</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>パスワード設定（UserService#resetPassword。saveAndFlush）</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ? FOR UPDATE;
+UPDATE users SET password_hash = ?, must_change_password = TRUE, password_changed_at = ?, failed_login_count = 0, locked_until = NULL WHERE id = ?
+※ 他の列は取得時の値のまま。password_changed_at は Asia/Tokyo の現在日時。updated_at は DB トリガで自動更新</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>7.3 設定値</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="49" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="F38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="49" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Asia/Tokyo</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>全処理共通。TIMESTAMP の JST 読み書き</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n"/>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>（コード定数）MAX_CHAIN_DEPTH</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>UserService</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>100（上長の連鎖を辿る最大段数）</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>データ破損時の無限ループ防止</t>
         </is>
       </c>
-      <c r="F35" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="C39:D39"/>
     <mergeCell ref="B30:F30"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
